--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -632,10 +632,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -647,6 +647,43 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -654,8 +691,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -671,30 +716,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -704,50 +726,6 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -767,6 +745,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -775,16 +761,30 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -796,6 +796,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -811,7 +817,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -823,7 +931,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -835,43 +961,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,103 +973,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -990,15 +990,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1028,11 +1019,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1061,6 +1050,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1076,17 +1080,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1098,145 +1098,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31">
         <v>1</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32">
         <v>1</v>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40">
         <v>1</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43">
         <v>1</v>
@@ -4286,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44">
         <v>1</v>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63">
         <v>1</v>
@@ -5526,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64">
         <v>1</v>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -632,38 +632,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -685,6 +662,88 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -700,61 +759,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -769,24 +775,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -799,7 +799,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -811,7 +811,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -823,7 +853,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -835,25 +877,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -865,25 +913,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,13 +937,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -913,49 +961,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -967,19 +979,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -990,15 +990,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1019,9 +1010,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1082,11 +1075,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1098,145 +1098,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="205">
   <si>
     <t>Id</t>
   </si>
@@ -607,6 +607,12 @@
   </si>
   <si>
     <t>戦闘不能を回避し反撃ダメージ</t>
+  </si>
+  <si>
+    <t>チャージ</t>
+  </si>
+  <si>
+    <t>次の行動でのフラグが立つ</t>
   </si>
   <si>
     <t>なし</t>
@@ -632,8 +638,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -643,102 +649,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -758,9 +668,74 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -775,7 +750,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -789,6 +764,37 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -799,7 +805,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -811,7 +817,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -823,7 +877,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -841,126 +967,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -973,13 +979,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -990,6 +996,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1004,17 +1019,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1037,23 +1041,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1077,16 +1066,33 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1098,7 +1104,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1107,7 +1113,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1116,127 +1122,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1563,7 +1569,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:S72"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -5976,6 +5982,68 @@
         <v>呪詛</v>
       </c>
     </row>
+    <row r="72" spans="1:19">
+      <c r="A72">
+        <v>3010</v>
+      </c>
+      <c r="B72">
+        <v>3010</v>
+      </c>
+      <c r="C72" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
+        <v>チャージ</v>
+      </c>
+      <c r="D72" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72" t="str">
+        <f>INDEX(Define!B:B,MATCH(E72,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72" t="str">
+        <f>TextData!B71</f>
+        <v>チャージ</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -5986,7 +6054,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -6760,6 +6828,17 @@
       </c>
       <c r="C70" t="s">
         <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
+        <v>3010</v>
+      </c>
+      <c r="B71" t="s">
+        <v>197</v>
+      </c>
+      <c r="C71" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -6784,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6792,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6800,7 +6879,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6808,7 +6887,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6816,7 +6895,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6824,7 +6903,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
